--- a/data/nav.xlsx
+++ b/data/nav.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -33,23 +33,14 @@
   <si>
     <t>expenses</t>
   </si>
-  <si>
-    <t>2024-09-30</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -102,11 +93,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -425,11 +417,11 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
+      <c r="A2" s="2">
+        <v>45322</v>
       </c>
       <c r="B2">
-        <v>95000000</v>
+        <v>101302375</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -438,62 +430,62 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-450000</v>
+        <v>-480000</v>
       </c>
       <c r="F2">
-        <v>-120000</v>
+        <v>-140000</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
+      <c r="A3" s="2">
+        <v>45351</v>
       </c>
       <c r="B3">
-        <v>97200000</v>
+        <v>105566458.3333333</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>-480000</v>
+      </c>
+      <c r="F3">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>45382</v>
+      </c>
+      <c r="B4">
+        <v>109830916.6666667</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>-480000</v>
+      </c>
+      <c r="F4">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>45412</v>
+      </c>
+      <c r="B5">
+        <v>115088666.6666667</v>
+      </c>
+      <c r="C5">
         <v>5000000</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>-460000</v>
-      </c>
-      <c r="F3">
-        <v>-125000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>99850000</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>-470000</v>
-      </c>
-      <c r="F4">
-        <v>-130000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>103200000</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
         <v>0</v>
       </c>
@@ -501,6 +493,166 @@
         <v>-480000</v>
       </c>
       <c r="F5">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>45443</v>
+      </c>
+      <c r="B6">
+        <v>112349500</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>-480000</v>
+      </c>
+      <c r="F6">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="B7">
+        <v>111723875.8333333</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>-480000</v>
+      </c>
+      <c r="F7">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B8">
+        <v>110037018.3333333</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>-480000</v>
+      </c>
+      <c r="F8">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>45535</v>
+      </c>
+      <c r="B9">
+        <v>109005629.5833333</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>-480000</v>
+      </c>
+      <c r="F9">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>45565</v>
+      </c>
+      <c r="B10">
+        <v>106684523.3333333</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>-480000</v>
+      </c>
+      <c r="F10">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>45596</v>
+      </c>
+      <c r="B11">
+        <v>102701725.4166667</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>2000000</v>
+      </c>
+      <c r="E11">
+        <v>-480000</v>
+      </c>
+      <c r="F11">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>45626</v>
+      </c>
+      <c r="B12">
+        <v>103720344.1666667</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>-480000</v>
+      </c>
+      <c r="F12">
+        <v>-140000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>45657</v>
+      </c>
+      <c r="B13">
+        <v>102238192.0833333</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>-480000</v>
+      </c>
+      <c r="F13">
         <v>-140000</v>
       </c>
     </row>
